--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="511">
   <si>
     <t>ID</t>
   </si>
@@ -106,7 +106,7 @@
     <t>Logo and login entry visible; at least 3 headline cards; story titles not empty</t>
   </si>
   <si>
-    <t>PASS</t>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>tests/web/home/home.spec.ts</t>
@@ -287,127 +287,6 @@
     <t>Facebook, Google, phone sign-in, "Lupa Password" and "Daftar Sekarang!" visible</t>
   </si>
   <si>
-    <t>TC-AUTH-008</t>
-  </si>
-  <si>
-    <t>Valid account logs in and the header shows the user</t>
-  </si>
-  <si>
-    <t>Manual (human-assisted: Cloudflare check)</t>
-  </si>
-  <si>
-    <t>Active accounts cannot log in</t>
-  </si>
-  <si>
-    <t>Registered account; human solves the Cloudflare check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open /login
-2. Enter the valid account
-3. Tick "Verify you are human"
-4. Click "Masuk"</t>
-  </si>
-  <si>
-    <t>Redirected away from /login; header shows the user instead of "Masuk"</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
-  </si>
-  <si>
-    <t>scripts/capture-session.ts</t>
-  </si>
-  <si>
-    <t>TC-AUTH-009</t>
-  </si>
-  <si>
-    <t>Wrong password is rejected with a clear message</t>
-  </si>
-  <si>
-    <t>Invalid accounts accepted, or rejected without a clear message</t>
-  </si>
-  <si>
-    <t>Registered email; human solves the Cloudflare check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open /login
-2. Enter the registered email and a wrong password
-3. Tick "Verify you are human"
-4. Click "Masuk"</t>
-  </si>
-  <si>
-    <t>Stays on /login with a clear error message; no session created</t>
-  </si>
-  <si>
-    <t>scripts/capture-session.ts --negative</t>
-  </si>
-  <si>
-    <t>TC-AUTH-010</t>
-  </si>
-  <si>
-    <t>Signed-in session survives a reload and a new tab</t>
-  </si>
-  <si>
-    <t>Planned (needs signed-in session)</t>
-  </si>
-  <si>
-    <t>Users logged out unexpectedly</t>
-  </si>
-  <si>
-    <t>Signed-in session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the homepage signed in
-2. Reload
-3. Open a new tab on the homepage</t>
-  </si>
-  <si>
-    <t>Header shows the user in all three</t>
-  </si>
-  <si>
-    <t>PLANNED</t>
-  </si>
-  <si>
-    <t>tests/web/auth/session.spec.ts</t>
-  </si>
-  <si>
-    <t>TC-AUTH-011</t>
-  </si>
-  <si>
-    <t>Signed-in user visiting /login is not shown the login form</t>
-  </si>
-  <si>
-    <t>Confusing double login</t>
-  </si>
-  <si>
-    <t>1. Open /login while signed in</t>
-  </si>
-  <si>
-    <t>Redirected away, or the form is not offered</t>
-  </si>
-  <si>
-    <t>TC-AUTH-012</t>
-  </si>
-  <si>
-    <t>Logout ends the session; liking requires login again</t>
-  </si>
-  <si>
-    <t>Session not terminated on shared devices</t>
-  </si>
-  <si>
-    <t>Signed-in session (in a separate context)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the account menu
-2. Click logout
-3. Open a story and tap like</t>
-  </si>
-  <si>
-    <t>Header shows "Masuk"; like redirects to /login</t>
-  </si>
-  <si>
-    <t>tests/web/auth/logout.spec.ts</t>
-  </si>
-  <si>
     <t>TC-ART-001</t>
   </si>
   <si>
@@ -469,9 +348,6 @@
   </si>
   <si>
     <t>HTTP 404; header still usable</t>
-  </si>
-  <si>
-    <t>FLAKY</t>
   </si>
   <si>
     <t>TC-ART-005</t>
@@ -490,67 +366,10 @@
     <t>Homepage with headlines</t>
   </si>
   <si>
-    <t>TC-LIKE-001</t>
+    <t>TC-LIKE-004</t>
   </si>
   <si>
     <t>Like</t>
-  </si>
-  <si>
-    <t>Signed-in like increments the count and activates the icon</t>
-  </si>
-  <si>
-    <t>Likes not recorded</t>
-  </si>
-  <si>
-    <t>Signed-in; story not yet liked by the account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open a story
-2. Tap like</t>
-  </si>
-  <si>
-    <t>Count +1; icon active (state reverted in teardown)</t>
-  </si>
-  <si>
-    <t>tests/web/engagement/like-signed-in.spec.ts</t>
-  </si>
-  <si>
-    <t>TC-LIKE-002</t>
-  </si>
-  <si>
-    <t>Unlike restores the original count</t>
-  </si>
-  <si>
-    <t>Counter drift</t>
-  </si>
-  <si>
-    <t>Signed-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Like a story
-2. Tap like again</t>
-  </si>
-  <si>
-    <t>Count back to the original; icon inactive</t>
-  </si>
-  <si>
-    <t>TC-LIKE-003</t>
-  </si>
-  <si>
-    <t>Like state survives a reload</t>
-  </si>
-  <si>
-    <t>Like stored only client-side</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Like a story
-2. Reload</t>
-  </si>
-  <si>
-    <t>Still liked with the incremented count (reverted in teardown)</t>
-  </si>
-  <si>
-    <t>TC-LIKE-004</t>
   </si>
   <si>
     <t>Guest who taps like is sent to login and the count does not change</t>
@@ -570,23 +389,6 @@
     <t>tests/web/engagement/like.spec.ts</t>
   </si>
   <si>
-    <t>TC-LIKE-005</t>
-  </si>
-  <si>
-    <t>Rapid double tap does not double count</t>
-  </si>
-  <si>
-    <t>Race condition inflates likes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open a story
-2. Tap like twice quickly
-3. Reload</t>
-  </si>
-  <si>
-    <t>Count is original or original +1, never +2</t>
-  </si>
-  <si>
     <t>TC-CMT-001</t>
   </si>
   <si>
@@ -625,69 +427,20 @@
     <t>Thread header shows "&lt;same count&gt; Komentar"; empty state when 0</t>
   </si>
   <si>
-    <t>TC-CMT-003</t>
-  </si>
-  <si>
-    <t>Signed-in user can compose a comment and send becomes available (not submitted)</t>
-  </si>
-  <si>
-    <t>Signed-in users cannot comment</t>
+    <t>TC-CMT-004</t>
+  </si>
+  <si>
+    <t>Guest typing a comment publishes nothing</t>
+  </si>
+  <si>
+    <t>Anonymous comments published (authorization)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open a thread
 2. Type a comment</t>
   </si>
   <si>
-    <t>Text kept; send button enabled. Not clicked (assignment rule)</t>
-  </si>
-  <si>
-    <t>tests/web/engagement/comment-signed-in.spec.ts</t>
-  </si>
-  <si>
-    <t>TC-CMT-004</t>
-  </si>
-  <si>
-    <t>Guest typing a comment publishes nothing</t>
-  </si>
-  <si>
-    <t>Anonymous comments published (authorization)</t>
-  </si>
-  <si>
     <t>No comment mutation sent; still on the thread. Observation OBS-001: no login prompt while drafting</t>
-  </si>
-  <si>
-    <t>TC-CMT-005</t>
-  </si>
-  <si>
-    <t>Empty or whitespace-only comment cannot be sent</t>
-  </si>
-  <si>
-    <t>Blank comments published</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open a thread
-2. Leave the editor empty, then type only spaces</t>
-  </si>
-  <si>
-    <t>Send unavailable or ignored (asserted without clicking a publishing send)</t>
-  </si>
-  <si>
-    <t>TC-CMT-006</t>
-  </si>
-  <si>
-    <t>Emoji, Indonesian text and line breaks are kept in the editor</t>
-  </si>
-  <si>
-    <t>Content mangled</t>
-  </si>
-  <si>
-    <t>"Mantap 👍\nTerima kasih"</t>
-  </si>
-  <si>
-    <t>1. Type multi-line text with emoji</t>
-  </si>
-  <si>
-    <t>Editor value identical to input</t>
   </si>
   <si>
     <t>TC-RPT-001</t>
@@ -846,9 +599,6 @@
   </si>
   <si>
     <t>User stays on kumparan (e.g. the story)</t>
-  </si>
-  <si>
-    <t>DEFECT</t>
   </si>
   <si>
     <t>BUG-001</t>
@@ -904,9 +654,6 @@
   </si>
   <si>
     <t>URL stays /report/story/&lt;slug&gt;</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
   </si>
   <si>
     <t>BUG-002</t>
@@ -1555,6 +1302,9 @@
     <t>200; no errors; post matches contract; author id 1</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
     <t>tests/api/graphql/queries.spec.ts</t>
   </si>
   <si>
@@ -1820,6 +1570,9 @@
   </si>
   <si>
     <t>post is null</t>
+  </si>
+  <si>
+    <t>DEFECT</t>
   </si>
   <si>
     <t>BUG-004</t>
@@ -1860,7 +1613,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1875,16 +1628,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1FADF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F4F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF0C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -1905,7 +1648,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1917,12 +1660,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2264,7 +2001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2381,19 +2118,19 @@
       <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>31</v>
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R2" s="2" t="s">
@@ -2440,19 +2177,19 @@
       <c r="L3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>31</v>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R3" s="2" t="s">
@@ -2499,11 +2236,11 @@
       <c r="L4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>31</v>
+      <c r="M4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -2511,7 +2248,7 @@
       <c r="P4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R4" s="2" t="s">
@@ -2558,19 +2295,19 @@
       <c r="L5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>31</v>
+      <c r="M5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R5" s="2" t="s">
@@ -2617,11 +2354,11 @@
       <c r="L6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>31</v>
+      <c r="M6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -2629,7 +2366,7 @@
       <c r="P6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R6" s="2" t="s">
@@ -2676,11 +2413,11 @@
       <c r="L7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>31</v>
+      <c r="M7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -2688,7 +2425,7 @@
       <c r="P7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" s="3" t="s">
+      <c r="Q7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R7" s="2" t="s">
@@ -2735,11 +2472,11 @@
       <c r="L8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>31</v>
+      <c r="M8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -2747,7 +2484,7 @@
       <c r="P8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="Q8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R8" s="2" t="s">
@@ -2794,11 +2531,11 @@
       <c r="L9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>31</v>
+      <c r="M9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -2806,7 +2543,7 @@
       <c r="P9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="Q9" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R9" s="2" t="s">
@@ -2853,11 +2590,11 @@
       <c r="L10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>31</v>
+      <c r="M10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -2865,7 +2602,7 @@
       <c r="P10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R10" s="2" t="s">
@@ -2912,11 +2649,11 @@
       <c r="L11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>31</v>
+      <c r="M11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -2924,7 +2661,7 @@
       <c r="P11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q11" s="3" t="s">
+      <c r="Q11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="R11" s="2" t="s">
@@ -2939,10 +2676,10 @@
         <v>88</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>22</v>
@@ -2954,16 +2691,16 @@
         <v>24</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>91</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>93</v>
@@ -2984,52 +2721,52 @@
         <v>28</v>
       </c>
       <c r="Q12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="M13" s="2" t="s">
         <v>28</v>
       </c>
@@ -3043,51 +2780,51 @@
         <v>28</v>
       </c>
       <c r="Q13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S13" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>28</v>
@@ -3101,28 +2838,28 @@
       <c r="P14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q14" s="4" t="s">
-        <v>111</v>
+      <c r="Q14" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R14" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>41</v>
@@ -3131,23 +2868,23 @@
         <v>24</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="I15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="M15" s="2" t="s">
         <v>28</v>
       </c>
@@ -3160,52 +2897,52 @@
       <c r="P15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q15" s="4" t="s">
-        <v>111</v>
+      <c r="Q15" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>28</v>
@@ -3219,28 +2956,28 @@
       <c r="P16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q16" s="4" t="s">
-        <v>111</v>
+      <c r="Q16" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>23</v>
@@ -3252,51 +2989,51 @@
         <v>25</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="M17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>22</v>
@@ -3311,51 +3048,51 @@
         <v>25</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="M18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>22</v>
@@ -3370,57 +3107,57 @@
         <v>25</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>24</v>
@@ -3429,57 +3166,57 @@
         <v>25</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="M20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N20" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>146</v>
-      </c>
       <c r="R20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>24</v>
@@ -3488,51 +3225,51 @@
         <v>25</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="M21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>22</v>
@@ -3544,22 +3281,22 @@
         <v>24</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>28</v>
@@ -3573,28 +3310,28 @@
       <c r="P22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q22" s="4" t="s">
-        <v>111</v>
+      <c r="Q22" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>23</v>
@@ -3603,22 +3340,22 @@
         <v>24</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>28</v>
@@ -3632,28 +3369,28 @@
       <c r="P23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q23" s="4" t="s">
-        <v>111</v>
+      <c r="Q23" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>41</v>
@@ -3662,22 +3399,22 @@
         <v>24</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>28</v>
@@ -3691,31 +3428,31 @@
       <c r="P24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q24" s="4" t="s">
-        <v>111</v>
+      <c r="Q24" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>24</v>
@@ -3724,78 +3461,78 @@
         <v>25</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="M25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>28</v>
@@ -3809,28 +3546,28 @@
       <c r="P26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q26" s="4" t="s">
-        <v>111</v>
+      <c r="Q26" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>23</v>
@@ -3842,57 +3579,57 @@
         <v>25</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="M27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>24</v>
@@ -3901,78 +3638,78 @@
         <v>25</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="M28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>28</v>
@@ -3986,31 +3723,31 @@
       <c r="P29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q29" s="4" t="s">
-        <v>111</v>
+      <c r="Q29" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>24</v>
@@ -4019,51 +3756,51 @@
         <v>25</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="M30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R30" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>68</v>
@@ -4075,22 +3812,22 @@
         <v>24</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>28</v>
@@ -4104,28 +3841,28 @@
       <c r="P31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q31" s="4" t="s">
-        <v>111</v>
+      <c r="Q31" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>79</v>
@@ -4134,22 +3871,22 @@
         <v>24</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>163</v>
+        <v>203</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>212</v>
+        <v>28</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>28</v>
@@ -4163,25 +3900,25 @@
       <c r="P32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q32" s="4" t="s">
-        <v>111</v>
+      <c r="Q32" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -4196,57 +3933,57 @@
         <v>25</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="M33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q33" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>24</v>
@@ -4255,54 +3992,54 @@
         <v>25</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q34" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>23</v>
@@ -4314,54 +4051,54 @@
         <v>25</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="M35" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>41</v>
@@ -4373,57 +4110,57 @@
         <v>25</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="M36" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q36" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>24</v>
@@ -4432,51 +4169,51 @@
         <v>25</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="M37" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>40</v>
@@ -4491,54 +4228,54 @@
         <v>25</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="M38" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q38" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>23</v>
@@ -4550,57 +4287,57 @@
         <v>25</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>28</v>
+        <v>245</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="M39" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q39" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>24</v>
@@ -4609,54 +4346,54 @@
         <v>25</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>27</v>
+        <v>252</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="M40" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>41</v>
@@ -4668,25 +4405,25 @@
         <v>25</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>266</v>
+        <v>259</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -4694,28 +4431,28 @@
       <c r="P41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q41" s="6" t="s">
-        <v>266</v>
+      <c r="Q41" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>267</v>
+        <v>28</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>41</v>
@@ -4727,51 +4464,51 @@
         <v>25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="M42" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q42" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R42" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>68</v>
@@ -4786,54 +4523,54 @@
         <v>25</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>225</v>
+        <v>27</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>275</v>
+        <v>28</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="M43" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q43" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R43" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>79</v>
@@ -4845,25 +4582,25 @@
         <v>25</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>281</v>
+        <v>27</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>28</v>
+        <v>274</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -4871,31 +4608,31 @@
       <c r="P44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q44" s="4" t="s">
-        <v>284</v>
+      <c r="Q44" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>285</v>
+        <v>28</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>24</v>
@@ -4904,57 +4641,57 @@
         <v>25</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>129</v>
+        <v>280</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="M45" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q45" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>24</v>
@@ -4963,57 +4700,57 @@
         <v>25</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>129</v>
+        <v>286</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="M46" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>24</v>
@@ -5022,57 +4759,57 @@
         <v>25</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>301</v>
+        <v>27</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>129</v>
+        <v>292</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="M47" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q47" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>24</v>
@@ -5081,57 +4818,57 @@
         <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>307</v>
+        <v>27</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="M48" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q48" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>24</v>
@@ -5140,7 +4877,7 @@
         <v>25</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>27</v>
@@ -5149,107 +4886,107 @@
         <v>28</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="M49" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q49" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R49" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I50" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S50" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>24</v>
@@ -5258,51 +4995,51 @@
         <v>25</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>324</v>
+        <v>28</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="M51" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q51" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R51" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>22</v>
@@ -5311,60 +5048,60 @@
         <v>41</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="M52" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q52" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>41</v>
@@ -5376,125 +5113,125 @@
         <v>25</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R53" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="J53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="S53" s="2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>342</v>
+        <v>28</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="M54" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R54" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>27</v>
@@ -5503,337 +5240,337 @@
         <v>28</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M55" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q55" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>352</v>
+        <v>262</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>353</v>
+        <v>28</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="M56" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q56" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q56" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>68</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="M57" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q57" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>365</v>
+        <v>28</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="M58" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q58" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R58" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>370</v>
+        <v>210</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>371</v>
+        <v>28</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="M59" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>40</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>377</v>
+        <v>28</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="M60" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q60" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P60" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R60" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
     </row>
     <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>22</v>
@@ -5842,13 +5579,13 @@
         <v>41</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>27</v>
@@ -5857,160 +5594,160 @@
         <v>28</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="M61" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q61" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>390</v>
+        <v>27</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N62" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q62" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O62" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R62" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
     </row>
     <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>395</v>
-      </c>
       <c r="I63" s="2" t="s">
-        <v>396</v>
+        <v>228</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="M63" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q63" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q63" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R63" s="2" t="s">
-        <v>28</v>
+        <v>384</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
     </row>
     <row r="64" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>22</v>
@@ -6019,945 +5756,945 @@
         <v>41</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>402</v>
+        <v>311</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M64" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q64" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N64" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="65" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>407</v>
+        <v>334</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="M65" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="N65" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q65" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q65" s="6" t="s">
-        <v>266</v>
-      </c>
       <c r="R65" s="2" t="s">
-        <v>410</v>
+        <v>28</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>25</v>
+        <v>339</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="I66" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S66" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M66" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>416</v>
+        <v>337</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>418</v>
+        <v>339</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>27</v>
+        <v>311</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="M67" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q67" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N67" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="O67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="R67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
     </row>
     <row r="68" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>341</v>
+        <v>408</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>28</v>
+        <v>410</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N68" s="4" t="s">
-        <v>284</v>
+        <v>412</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P68" s="2" t="s">
-        <v>28</v>
+      <c r="P68" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="69" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="D69" s="2" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J69" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="H69" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="K69" s="2" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N69" s="4" t="s">
-        <v>284</v>
+        <v>420</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P69" s="2" t="s">
-        <v>28</v>
+      <c r="P69" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R69" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="70" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N70" s="4" t="s">
-        <v>284</v>
+        <v>425</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>28</v>
+      <c r="P70" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="71" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>289</v>
+        <v>428</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N71" s="4" t="s">
-        <v>284</v>
+        <v>430</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P71" s="2" t="s">
-        <v>28</v>
+      <c r="P71" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
     </row>
     <row r="72" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>28</v>
+        <v>434</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>284</v>
+        <v>436</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P72" s="2" t="s">
-        <v>28</v>
+      <c r="P72" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
     </row>
     <row r="73" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>449</v>
+        <v>257</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N73" s="4" t="s">
-        <v>284</v>
+        <v>440</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P73" s="2" t="s">
-        <v>28</v>
+      <c r="P73" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
     </row>
     <row r="74" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>41</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N74" s="4" t="s">
-        <v>284</v>
+        <v>445</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P74" s="2" t="s">
-        <v>28</v>
+      <c r="P74" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R74" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>307</v>
+        <v>409</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="M75" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="N75" s="4" t="s">
-        <v>284</v>
+        <v>450</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q75" s="6" t="s">
-        <v>266</v>
+      <c r="P75" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q75" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>463</v>
+        <v>28</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="76" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>31</v>
+        <v>456</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P76" s="2" t="s">
-        <v>28</v>
+      <c r="P76" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R76" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H77" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P77" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="M77" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P77" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="Q77" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R77" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>31</v>
+        <v>466</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P78" s="2" t="s">
-        <v>28</v>
+      <c r="P78" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R78" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>390</v>
+        <v>409</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="M79" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>31</v>
+        <v>471</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P79" s="2" t="s">
-        <v>28</v>
+      <c r="P79" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R79" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="80" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>23</v>
@@ -6969,19 +6706,19 @@
         <v>25</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>489</v>
+        <v>28</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>491</v>
+        <v>477</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>28</v>
@@ -6993,30 +6730,30 @@
         <v>28</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="81" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>23</v>
@@ -7028,19 +6765,19 @@
         <v>25</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>496</v>
+        <v>28</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>28</v>
@@ -7052,33 +6789,33 @@
         <v>28</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R81" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>15</v>
@@ -7087,19 +6824,19 @@
         <v>25</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>28</v>
@@ -7111,33 +6848,33 @@
         <v>28</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R82" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>15</v>
@@ -7146,19 +6883,19 @@
         <v>25</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>28</v>
@@ -7170,30 +6907,30 @@
         <v>28</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R83" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="84" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>41</v>
@@ -7205,19 +6942,19 @@
         <v>25</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>512</v>
+        <v>28</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>28</v>
@@ -7229,33 +6966,33 @@
         <v>28</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="R84" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>15</v>
@@ -7264,19 +7001,19 @@
         <v>25</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>336</v>
+        <v>500</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>28</v>
@@ -7287,28 +7024,28 @@
       <c r="O85" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P85" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q85" s="3" t="s">
-        <v>31</v>
+      <c r="P85" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q85" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>28</v>
+        <v>504</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="86" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>485</v>
+        <v>406</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>68</v>
@@ -7323,19 +7060,19 @@
         <v>25</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>28</v>
@@ -7346,725 +7083,17 @@
       <c r="O86" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P86" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q86" s="3" t="s">
-        <v>31</v>
+      <c r="P86" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q86" s="4" t="s">
+        <v>503</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>28</v>
+        <v>510</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q87" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S87" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N88" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q88" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R88" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S88" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R89" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S89" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="M90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q90" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S90" s="2" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="M91" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N91" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R91" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S91" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="M92" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N92" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q92" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R92" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S92" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="M93" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N93" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O93" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q93" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R93" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S93" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R94" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S94" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q95" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R95" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S95" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="M96" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N96" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q96" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R96" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N97" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O97" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q97" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="R97" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="S97" s="2" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N98" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="R98" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>550</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -106,7 +106,7 @@
     <t>Logo and login entry visible; at least 3 headline cards; story titles not empty</t>
   </si>
   <si>
-    <t>NOT RUN</t>
+    <t>PASS</t>
   </si>
   <si>
     <t>tests/web/home/home.spec.ts</t>
@@ -585,20 +585,23 @@
     <t>TC-RPT-009</t>
   </si>
   <si>
-    <t>Cancel on a directly opened report link keeps the user on kumparan</t>
-  </si>
-  <si>
-    <t>Users lost on a blank page</t>
-  </si>
-  <si>
-    <t>Report form opened from a shared/bookmarked link (no history)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open /report/story/&lt;slug&gt; directly
+    <t>"Batal" on a report link opened in a new tab takes the reader out of the form</t>
+  </si>
+  <si>
+    <t>Readers stuck on the form (dead Cancel button)</t>
+  </si>
+  <si>
+    <t>Report link opened in a new tab (history.length 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open /report/story/&lt;slug&gt; in a new tab
 2. Click "Batal"</t>
   </si>
   <si>
-    <t>User stays on kumparan (e.g. the story)</t>
+    <t>Reader leaves the form (e.g. back to the story)</t>
+  </si>
+  <si>
+    <t>DEFECT</t>
   </si>
   <si>
     <t>BUG-001</t>
@@ -639,21 +642,24 @@
     <t>TC-RPT-012</t>
   </si>
   <si>
-    <t>Report form keeps its own URL after opening from a story</t>
+    <t>Keyboard user opening the report form keeps the form URL in the address bar</t>
   </si>
   <si>
     <t>Refresh/share leads to a different page than shown</t>
   </si>
   <si>
-    <t>Story read to the end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Scroll to the end of a story
-2. Open the report form
+    <t>Story open on desktop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Focus "Laporkan tulisan" with the keyboard
+2. Press Enter
 3. Watch the address bar for 4 s</t>
   </si>
   <si>
     <t>URL stays /report/story/&lt;slug&gt;</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
   </si>
   <si>
     <t>BUG-002</t>
@@ -1302,9 +1308,6 @@
     <t>200; no errors; post matches contract; author id 1</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>tests/api/graphql/queries.spec.ts</t>
   </si>
   <si>
@@ -1570,9 +1573,6 @@
   </si>
   <si>
     <t>post is null</t>
-  </si>
-  <si>
-    <t>DEFECT</t>
   </si>
   <si>
     <t>BUG-004</t>
@@ -1613,7 +1613,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1635,6 +1635,11 @@
         <fgColor rgb="FFFEE4E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F4F7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1648,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1660,6 +1665,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2118,19 +2126,19 @@
       <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
+      <c r="M2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R2" s="2" t="s">
@@ -2177,19 +2185,19 @@
       <c r="L3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R3" s="2" t="s">
@@ -2236,11 +2244,11 @@
       <c r="L4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>28</v>
+      <c r="M4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -2248,7 +2256,7 @@
       <c r="P4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R4" s="2" t="s">
@@ -2295,19 +2303,19 @@
       <c r="L5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>28</v>
+      <c r="M5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R5" s="2" t="s">
@@ -2354,11 +2362,11 @@
       <c r="L6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>28</v>
+      <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -2366,7 +2374,7 @@
       <c r="P6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R6" s="2" t="s">
@@ -2413,11 +2421,11 @@
       <c r="L7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>28</v>
+      <c r="M7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -2425,7 +2433,7 @@
       <c r="P7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R7" s="2" t="s">
@@ -2472,11 +2480,11 @@
       <c r="L8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>28</v>
+      <c r="M8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>28</v>
@@ -2484,7 +2492,7 @@
       <c r="P8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R8" s="2" t="s">
@@ -2531,11 +2539,11 @@
       <c r="L9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>28</v>
+      <c r="M9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>28</v>
@@ -2543,7 +2551,7 @@
       <c r="P9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R9" s="2" t="s">
@@ -2590,11 +2598,11 @@
       <c r="L10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>28</v>
+      <c r="M10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>28</v>
@@ -2602,7 +2610,7 @@
       <c r="P10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R10" s="2" t="s">
@@ -2649,11 +2657,11 @@
       <c r="L11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>28</v>
+      <c r="M11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -2661,7 +2669,7 @@
       <c r="P11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R11" s="2" t="s">
@@ -2708,19 +2716,19 @@
       <c r="L12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>28</v>
+      <c r="M12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="Q12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R12" s="2" t="s">
@@ -2767,19 +2775,19 @@
       <c r="L13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>28</v>
+      <c r="M13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="Q13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R13" s="2" t="s">
@@ -2826,11 +2834,11 @@
       <c r="L14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>28</v>
+      <c r="M14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2838,7 +2846,7 @@
       <c r="P14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="Q14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R14" s="2" t="s">
@@ -2885,11 +2893,11 @@
       <c r="L15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>28</v>
+      <c r="M15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -2897,7 +2905,7 @@
       <c r="P15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="Q15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R15" s="2" t="s">
@@ -2944,11 +2952,11 @@
       <c r="L16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>28</v>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -2956,7 +2964,7 @@
       <c r="P16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="Q16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R16" s="2" t="s">
@@ -3003,11 +3011,11 @@
       <c r="L17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>28</v>
+      <c r="M17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -3015,7 +3023,7 @@
       <c r="P17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="Q17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R17" s="2" t="s">
@@ -3062,19 +3070,19 @@
       <c r="L18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>28</v>
+      <c r="M18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="Q18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R18" s="2" t="s">
@@ -3121,11 +3129,11 @@
       <c r="L19" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>28</v>
+      <c r="M19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -3133,7 +3141,7 @@
       <c r="P19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="Q19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R19" s="2" t="s">
@@ -3180,11 +3188,11 @@
       <c r="L20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>28</v>
+      <c r="M20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -3192,7 +3200,7 @@
       <c r="P20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="Q20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R20" s="2" t="s">
@@ -3239,11 +3247,11 @@
       <c r="L21" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>28</v>
+      <c r="M21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -3251,7 +3259,7 @@
       <c r="P21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="Q21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R21" s="2" t="s">
@@ -3298,11 +3306,11 @@
       <c r="L22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>28</v>
+      <c r="M22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -3310,7 +3318,7 @@
       <c r="P22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="Q22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R22" s="2" t="s">
@@ -3357,11 +3365,11 @@
       <c r="L23" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>28</v>
+      <c r="M23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>28</v>
@@ -3369,7 +3377,7 @@
       <c r="P23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="Q23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R23" s="2" t="s">
@@ -3416,11 +3424,11 @@
       <c r="L24" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>28</v>
+      <c r="M24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -3428,7 +3436,7 @@
       <c r="P24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="Q24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R24" s="2" t="s">
@@ -3475,11 +3483,11 @@
       <c r="L25" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>28</v>
+      <c r="M25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -3487,7 +3495,7 @@
       <c r="P25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="Q25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R25" s="2" t="s">
@@ -3534,11 +3542,11 @@
       <c r="L26" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>28</v>
+      <c r="M26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -3546,7 +3554,7 @@
       <c r="P26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="Q26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R26" s="2" t="s">
@@ -3593,11 +3601,11 @@
       <c r="L27" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>28</v>
+      <c r="M27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -3605,7 +3613,7 @@
       <c r="P27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="Q27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R27" s="2" t="s">
@@ -3652,11 +3660,11 @@
       <c r="L28" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>28</v>
+      <c r="M28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -3664,7 +3672,7 @@
       <c r="P28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="Q28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R28" s="2" t="s">
@@ -3711,11 +3719,11 @@
       <c r="L29" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>28</v>
+      <c r="M29" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -3723,11 +3731,11 @@
       <c r="P29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q29" s="2" t="s">
-        <v>31</v>
+      <c r="Q29" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="S29" s="2" t="s">
         <v>144</v>
@@ -3735,13 +3743,13 @@
     </row>
     <row r="30" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>68</v>
@@ -3756,7 +3764,7 @@
         <v>25</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>148</v>
@@ -3765,16 +3773,16 @@
         <v>28</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>28</v>
+      <c r="M30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -3782,7 +3790,7 @@
       <c r="P30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="Q30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R30" s="2" t="s">
@@ -3794,13 +3802,13 @@
     </row>
     <row r="31" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>68</v>
@@ -3815,25 +3823,25 @@
         <v>25</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>148</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>28</v>
+        <v>200</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -3841,7 +3849,7 @@
       <c r="P31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="Q31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R31" s="2" t="s">
@@ -3853,13 +3861,13 @@
     </row>
     <row r="32" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>40</v>
@@ -3868,31 +3876,31 @@
         <v>79</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>28</v>
+        <v>206</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -3900,11 +3908,11 @@
       <c r="P32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q32" s="2" t="s">
-        <v>31</v>
+      <c r="Q32" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>144</v>
@@ -3912,13 +3920,13 @@
     </row>
     <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -3933,7 +3941,7 @@
         <v>25</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>27</v>
@@ -3942,16 +3950,16 @@
         <v>92</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>28</v>
+        <v>214</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -3959,25 +3967,25 @@
       <c r="P33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="Q33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>22</v>
@@ -3992,7 +4000,7 @@
         <v>25</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>27</v>
@@ -4001,16 +4009,16 @@
         <v>92</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>28</v>
+        <v>220</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -4018,25 +4026,25 @@
       <c r="P34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="Q34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>22</v>
@@ -4051,25 +4059,25 @@
         <v>25</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>92</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>28</v>
+        <v>226</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -4077,25 +4085,25 @@
       <c r="P35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="Q35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>22</v>
@@ -4110,25 +4118,25 @@
         <v>25</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>28</v>
+        <v>232</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -4136,25 +4144,25 @@
       <c r="P36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="Q36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>40</v>
@@ -4169,7 +4177,7 @@
         <v>25</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>27</v>
@@ -4178,16 +4186,16 @@
         <v>28</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>28</v>
+        <v>237</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -4195,25 +4203,25 @@
       <c r="P37" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="Q37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R37" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>40</v>
@@ -4228,25 +4236,25 @@
         <v>25</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>28</v>
+        <v>242</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -4254,25 +4262,25 @@
       <c r="P38" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="Q38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>22</v>
@@ -4287,51 +4295,51 @@
         <v>25</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>28</v>
+        <v>249</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="Q39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>22</v>
@@ -4346,25 +4354,25 @@
         <v>25</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>28</v>
+        <v>256</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -4372,25 +4380,25 @@
       <c r="P40" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q40" s="2" t="s">
+      <c r="Q40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>22</v>
@@ -4405,25 +4413,25 @@
         <v>25</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>28</v>
+        <v>261</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -4431,25 +4439,25 @@
       <c r="P41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q41" s="2" t="s">
+      <c r="Q41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>55</v>
@@ -4464,25 +4472,25 @@
         <v>25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>28</v>
+        <v>267</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -4490,25 +4498,25 @@
       <c r="P42" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q42" s="2" t="s">
+      <c r="Q42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>68</v>
@@ -4523,7 +4531,7 @@
         <v>25</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>27</v>
@@ -4532,16 +4540,16 @@
         <v>28</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>28</v>
+        <v>272</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -4549,25 +4557,25 @@
       <c r="P43" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="Q43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R43" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>68</v>
@@ -4582,25 +4590,25 @@
         <v>25</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>28</v>
+        <v>278</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -4608,25 +4616,25 @@
       <c r="P44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q44" s="2" t="s">
+      <c r="Q44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>68</v>
@@ -4641,25 +4649,25 @@
         <v>25</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>28</v>
+        <v>284</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -4667,25 +4675,25 @@
       <c r="P45" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q45" s="2" t="s">
+      <c r="Q45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>40</v>
@@ -4700,25 +4708,25 @@
         <v>25</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>28</v>
+        <v>290</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -4726,25 +4734,25 @@
       <c r="P46" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="Q46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>40</v>
@@ -4759,25 +4767,25 @@
         <v>25</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>28</v>
+        <v>296</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -4785,25 +4793,25 @@
       <c r="P47" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q47" s="2" t="s">
+      <c r="Q47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>40</v>
@@ -4818,25 +4826,25 @@
         <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>28</v>
+        <v>302</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -4844,25 +4852,25 @@
       <c r="P48" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q48" s="2" t="s">
+      <c r="Q48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>22</v>
@@ -4877,7 +4885,7 @@
         <v>25</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>27</v>
@@ -4886,16 +4894,16 @@
         <v>28</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>28</v>
+        <v>308</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -4903,25 +4911,25 @@
       <c r="P49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q49" s="2" t="s">
+      <c r="Q49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R49" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>22</v>
@@ -4936,25 +4944,25 @@
         <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>28</v>
+        <v>315</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -4962,25 +4970,25 @@
       <c r="P50" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q50" s="2" t="s">
+      <c r="Q50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R50" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>22</v>
@@ -4995,25 +5003,25 @@
         <v>25</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>28</v>
+        <v>321</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -5021,25 +5029,25 @@
       <c r="P51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q51" s="2" t="s">
+      <c r="Q51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R51" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>22</v>
@@ -5054,25 +5062,25 @@
         <v>25</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>28</v>
+        <v>327</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -5080,25 +5088,25 @@
       <c r="P52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q52" s="2" t="s">
+      <c r="Q52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>40</v>
@@ -5113,7 +5121,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>27</v>
@@ -5122,16 +5130,16 @@
         <v>28</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>28</v>
+        <v>332</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -5139,25 +5147,25 @@
       <c r="P53" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q53" s="2" t="s">
-        <v>31</v>
+      <c r="Q53" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>22</v>
@@ -5172,25 +5180,25 @@
         <v>25</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>28</v>
+        <v>327</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -5198,25 +5206,25 @@
       <c r="P54" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q54" s="2" t="s">
+      <c r="Q54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>22</v>
@@ -5228,10 +5236,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>27</v>
@@ -5240,16 +5248,16 @@
         <v>28</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>28</v>
+        <v>344</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N55" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -5257,25 +5265,25 @@
       <c r="P55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q55" s="2" t="s">
+      <c r="Q55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R55" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>55</v>
@@ -5287,10 +5295,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>27</v>
@@ -5299,16 +5307,16 @@
         <v>28</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>28</v>
+        <v>349</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N56" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -5316,25 +5324,25 @@
       <c r="P56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q56" s="2" t="s">
+      <c r="Q56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>68</v>
@@ -5346,10 +5354,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>27</v>
@@ -5358,16 +5366,16 @@
         <v>28</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>28</v>
+        <v>354</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N57" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -5375,25 +5383,25 @@
       <c r="P57" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q57" s="2" t="s">
+      <c r="Q57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>40</v>
@@ -5405,10 +5413,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>27</v>
@@ -5417,16 +5425,16 @@
         <v>28</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>28</v>
+        <v>359</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N58" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -5434,25 +5442,25 @@
       <c r="P58" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q58" s="2" t="s">
+      <c r="Q58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R58" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>22</v>
@@ -5464,10 +5472,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>27</v>
@@ -5476,16 +5484,16 @@
         <v>28</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N59" s="2" t="s">
-        <v>28</v>
+        <v>363</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N59" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>28</v>
@@ -5493,25 +5501,25 @@
       <c r="P59" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q59" s="2" t="s">
+      <c r="Q59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>40</v>
@@ -5523,10 +5531,10 @@
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>27</v>
@@ -5535,16 +5543,16 @@
         <v>28</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>28</v>
+        <v>369</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N60" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -5552,25 +5560,25 @@
       <c r="P60" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q60" s="2" t="s">
+      <c r="Q60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>22</v>
@@ -5582,10 +5590,10 @@
         <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>27</v>
@@ -5594,16 +5602,16 @@
         <v>28</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>28</v>
+        <v>374</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -5611,25 +5619,25 @@
       <c r="P61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q61" s="2" t="s">
+      <c r="Q61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>40</v>
@@ -5641,10 +5649,10 @@
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>27</v>
@@ -5653,16 +5661,16 @@
         <v>28</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>28</v>
+        <v>380</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>28</v>
@@ -5670,25 +5678,25 @@
       <c r="P62" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q62" s="2" t="s">
+      <c r="Q62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R62" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>55</v>
@@ -5700,28 +5708,28 @@
         <v>12</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N63" s="2" t="s">
-        <v>28</v>
+        <v>385</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="N63" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -5729,25 +5737,25 @@
       <c r="P63" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q63" s="2" t="s">
-        <v>31</v>
+      <c r="Q63" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="64" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>22</v>
@@ -5759,28 +5767,28 @@
         <v>13</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>28</v>
+        <v>391</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>28</v>
@@ -5788,25 +5796,25 @@
       <c r="P64" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q64" s="2" t="s">
+      <c r="Q64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R64" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>22</v>
@@ -5818,28 +5826,28 @@
         <v>13</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>28</v>
+        <v>396</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>28</v>
@@ -5847,25 +5855,25 @@
       <c r="P65" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q65" s="2" t="s">
+      <c r="Q65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>22</v>
@@ -5877,28 +5885,28 @@
         <v>13</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>28</v>
+        <v>401</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>
@@ -5906,25 +5914,25 @@
       <c r="P66" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q66" s="2" t="s">
+      <c r="Q66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R66" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>22</v>
@@ -5936,28 +5944,28 @@
         <v>13</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>28</v>
+        <v>406</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>28</v>
@@ -5965,25 +5973,25 @@
       <c r="P67" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Q67" s="2" t="s">
+      <c r="Q67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="R67" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>22</v>
@@ -5998,19 +6006,19 @@
         <v>25</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>28</v>
@@ -6022,27 +6030,27 @@
         <v>28</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R68" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="69" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>22</v>
@@ -6057,19 +6065,19 @@
         <v>25</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>28</v>
@@ -6081,27 +6089,27 @@
         <v>28</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R69" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="70" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>22</v>
@@ -6116,19 +6124,19 @@
         <v>25</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>28</v>
@@ -6140,27 +6148,27 @@
         <v>28</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R70" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="71" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>22</v>
@@ -6175,19 +6183,19 @@
         <v>25</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>28</v>
@@ -6199,27 +6207,27 @@
         <v>28</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R71" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="72" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>22</v>
@@ -6234,19 +6242,19 @@
         <v>25</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>28</v>
@@ -6258,27 +6266,27 @@
         <v>28</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="73" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>22</v>
@@ -6293,19 +6301,19 @@
         <v>25</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>28</v>
@@ -6317,27 +6325,27 @@
         <v>28</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="74" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>68</v>
@@ -6352,19 +6360,19 @@
         <v>25</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>28</v>
@@ -6376,27 +6384,27 @@
         <v>28</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R74" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="75" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>22</v>
@@ -6411,19 +6419,19 @@
         <v>25</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>28</v>
@@ -6435,27 +6443,27 @@
         <v>28</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R75" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="76" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>22</v>
@@ -6470,19 +6478,19 @@
         <v>25</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>28</v>
@@ -6494,27 +6502,27 @@
         <v>28</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R76" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="77" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>22</v>
@@ -6529,19 +6537,19 @@
         <v>25</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>28</v>
@@ -6553,27 +6561,27 @@
         <v>28</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R77" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>55</v>
@@ -6588,19 +6596,19 @@
         <v>25</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>28</v>
@@ -6612,27 +6620,27 @@
         <v>28</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R78" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>55</v>
@@ -6647,19 +6655,19 @@
         <v>25</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>28</v>
@@ -6671,27 +6679,27 @@
         <v>28</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R79" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>55</v>
@@ -6706,19 +6714,19 @@
         <v>25</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>28</v>
@@ -6730,27 +6738,27 @@
         <v>28</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="81" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>55</v>
@@ -6765,19 +6773,19 @@
         <v>25</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>28</v>
@@ -6789,27 +6797,27 @@
         <v>28</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R81" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="82" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>55</v>
@@ -6824,19 +6832,19 @@
         <v>25</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>28</v>
@@ -6848,27 +6856,27 @@
         <v>28</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R82" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>40</v>
@@ -6883,19 +6891,19 @@
         <v>25</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>28</v>
@@ -6907,27 +6915,27 @@
         <v>28</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R83" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>55</v>
@@ -6942,19 +6950,19 @@
         <v>25</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>28</v>
@@ -6966,27 +6974,27 @@
         <v>28</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="R84" s="2" t="s">
         <v>28</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="85" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>68</v>
@@ -7001,19 +7009,19 @@
         <v>25</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>28</v>
@@ -7025,16 +7033,16 @@
         <v>28</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>503</v>
+        <v>189</v>
       </c>
       <c r="Q85" s="4" t="s">
-        <v>503</v>
+        <v>189</v>
       </c>
       <c r="R85" s="2" t="s">
         <v>504</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="86" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7042,7 +7050,7 @@
         <v>505</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>506</v>
@@ -7063,7 +7071,7 @@
         <v>507</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>28</v>
@@ -7084,16 +7092,16 @@
         <v>28</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>503</v>
+        <v>189</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>503</v>
+        <v>189</v>
       </c>
       <c r="R86" s="2" t="s">
         <v>510</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="510">
   <si>
     <t>ID</t>
   </si>
@@ -657,9 +657,6 @@
   </si>
   <si>
     <t>URL stays /report/story/&lt;slug&gt;</t>
-  </si>
-  <si>
-    <t>SKIPPED</t>
   </si>
   <si>
     <t>BUG-002</t>
@@ -1613,7 +1610,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1635,11 +1632,6 @@
         <fgColor rgb="FFFEE4E2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F4F7"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1653,7 +1645,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1665,9 +1657,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3899,8 +3888,8 @@
       <c r="M32" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="N32" s="5" t="s">
-        <v>207</v>
+      <c r="N32" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -3912,7 +3901,7 @@
         <v>189</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>144</v>
@@ -3920,13 +3909,13 @@
     </row>
     <row r="33" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -3941,7 +3930,7 @@
         <v>25</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>27</v>
@@ -3950,42 +3939,42 @@
         <v>92</v>
       </c>
       <c r="K33" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S33" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>22</v>
@@ -4000,7 +3989,7 @@
         <v>25</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>27</v>
@@ -4009,11 +3998,11 @@
         <v>92</v>
       </c>
       <c r="K34" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="M34" s="3" t="s">
         <v>31</v>
       </c>
@@ -4033,18 +4022,18 @@
         <v>28</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>22</v>
@@ -4059,20 +4048,20 @@
         <v>25</v>
       </c>
       <c r="H35" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>92</v>
       </c>
       <c r="K35" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>31</v>
       </c>
@@ -4092,18 +4081,18 @@
         <v>28</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>22</v>
@@ -4118,20 +4107,20 @@
         <v>25</v>
       </c>
       <c r="H36" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="J36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="L36" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="M36" s="3" t="s">
         <v>31</v>
       </c>
@@ -4151,18 +4140,18 @@
         <v>28</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>40</v>
@@ -4177,7 +4166,7 @@
         <v>25</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>27</v>
@@ -4186,11 +4175,11 @@
         <v>28</v>
       </c>
       <c r="K37" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="M37" s="3" t="s">
         <v>31</v>
       </c>
@@ -4210,18 +4199,18 @@
         <v>28</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>40</v>
@@ -4236,20 +4225,20 @@
         <v>25</v>
       </c>
       <c r="H38" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K38" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="M38" s="3" t="s">
         <v>31</v>
       </c>
@@ -4269,18 +4258,18 @@
         <v>28</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>22</v>
@@ -4295,51 +4284,51 @@
         <v>25</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J39" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S39" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>22</v>
@@ -4354,20 +4343,20 @@
         <v>25</v>
       </c>
       <c r="H40" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I40" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="J40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="J40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="M40" s="3" t="s">
         <v>31</v>
       </c>
@@ -4387,18 +4376,18 @@
         <v>28</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>22</v>
@@ -4413,20 +4402,20 @@
         <v>25</v>
       </c>
       <c r="H41" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K41" s="2" t="s">
+      <c r="L41" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>31</v>
       </c>
@@ -4446,18 +4435,18 @@
         <v>28</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>55</v>
@@ -4472,20 +4461,20 @@
         <v>25</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J42" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>31</v>
       </c>
@@ -4505,18 +4494,18 @@
         <v>28</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>68</v>
@@ -4531,7 +4520,7 @@
         <v>25</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>27</v>
@@ -4540,11 +4529,11 @@
         <v>28</v>
       </c>
       <c r="K43" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="L43" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>31</v>
       </c>
@@ -4564,18 +4553,18 @@
         <v>28</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>68</v>
@@ -4590,20 +4579,20 @@
         <v>25</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J44" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="L44" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>31</v>
       </c>
@@ -4623,18 +4612,18 @@
         <v>28</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>68</v>
@@ -4649,20 +4638,20 @@
         <v>25</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J45" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K45" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>31</v>
       </c>
@@ -4682,18 +4671,18 @@
         <v>28</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>40</v>
@@ -4708,20 +4697,20 @@
         <v>25</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J46" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K46" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>31</v>
       </c>
@@ -4741,18 +4730,18 @@
         <v>28</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>40</v>
@@ -4767,20 +4756,20 @@
         <v>25</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J47" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K47" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>31</v>
       </c>
@@ -4800,18 +4789,18 @@
         <v>28</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>40</v>
@@ -4826,20 +4815,20 @@
         <v>25</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J48" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K48" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="L48" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>31</v>
       </c>
@@ -4859,18 +4848,18 @@
         <v>28</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>22</v>
@@ -4885,7 +4874,7 @@
         <v>25</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>27</v>
@@ -4894,42 +4883,42 @@
         <v>28</v>
       </c>
       <c r="K49" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S49" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>22</v>
@@ -4944,22 +4933,22 @@
         <v>25</v>
       </c>
       <c r="H50" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I50" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="I50" s="2" t="s">
+      <c r="J50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="J50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K50" s="2" t="s">
+      <c r="L50" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="L50" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>207</v>
+      <c r="M50" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="N50" s="3" t="s">
         <v>31</v>
@@ -4977,18 +4966,18 @@
         <v>28</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>22</v>
@@ -5003,20 +4992,20 @@
         <v>25</v>
       </c>
       <c r="H51" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="J51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="J51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K51" s="2" t="s">
+      <c r="L51" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="L51" s="2" t="s">
-        <v>321</v>
-      </c>
       <c r="M51" s="3" t="s">
         <v>31</v>
       </c>
@@ -5036,18 +5025,18 @@
         <v>28</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>22</v>
@@ -5062,25 +5051,25 @@
         <v>25</v>
       </c>
       <c r="H52" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="J52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="J52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K52" s="2" t="s">
+      <c r="L52" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N52" s="5" t="s">
-        <v>207</v>
+      <c r="N52" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -5095,18 +5084,18 @@
         <v>28</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>40</v>
@@ -5121,7 +5110,7 @@
         <v>25</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>27</v>
@@ -5130,10 +5119,10 @@
         <v>28</v>
       </c>
       <c r="K53" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L53" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>189</v>
@@ -5151,21 +5140,21 @@
         <v>189</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>22</v>
@@ -5180,22 +5169,22 @@
         <v>25</v>
       </c>
       <c r="H54" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="L54" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>207</v>
+        <v>326</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>31</v>
@@ -5213,18 +5202,18 @@
         <v>28</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>22</v>
@@ -5236,10 +5225,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>27</v>
@@ -5248,42 +5237,42 @@
         <v>28</v>
       </c>
       <c r="K55" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="L55" s="2" t="s">
+      <c r="M55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S55" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N55" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R55" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>55</v>
@@ -5295,10 +5284,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>27</v>
@@ -5307,16 +5296,16 @@
         <v>28</v>
       </c>
       <c r="K56" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="M56" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N56" s="5" t="s">
-        <v>207</v>
+      <c r="N56" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -5331,18 +5320,18 @@
         <v>28</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="57" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>68</v>
@@ -5354,10 +5343,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>27</v>
@@ -5366,16 +5355,16 @@
         <v>28</v>
       </c>
       <c r="K57" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N57" s="5" t="s">
-        <v>207</v>
+      <c r="N57" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -5390,18 +5379,18 @@
         <v>28</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>40</v>
@@ -5413,10 +5402,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>27</v>
@@ -5425,16 +5414,16 @@
         <v>28</v>
       </c>
       <c r="K58" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L58" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="L58" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N58" s="5" t="s">
-        <v>207</v>
+      <c r="N58" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -5449,18 +5438,18 @@
         <v>28</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>22</v>
@@ -5472,10 +5461,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>27</v>
@@ -5484,42 +5473,42 @@
         <v>28</v>
       </c>
       <c r="K59" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="L59" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="L59" s="2" t="s">
+      <c r="M59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S59" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N59" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R59" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>40</v>
@@ -5531,10 +5520,10 @@
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>27</v>
@@ -5543,16 +5532,16 @@
         <v>28</v>
       </c>
       <c r="K60" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="L60" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="L60" s="2" t="s">
-        <v>369</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N60" s="5" t="s">
-        <v>207</v>
+      <c r="N60" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -5567,18 +5556,18 @@
         <v>28</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>22</v>
@@ -5590,10 +5579,10 @@
         <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>27</v>
@@ -5602,42 +5591,42 @@
         <v>28</v>
       </c>
       <c r="K61" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="L61" s="2" t="s">
+      <c r="M61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S61" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R61" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S61" s="2" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="62" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>40</v>
@@ -5649,10 +5638,10 @@
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>27</v>
@@ -5661,16 +5650,16 @@
         <v>28</v>
       </c>
       <c r="K62" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="L62" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="L62" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N62" s="5" t="s">
-        <v>207</v>
+      <c r="N62" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>28</v>
@@ -5685,18 +5674,18 @@
         <v>28</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>55</v>
@@ -5708,28 +5697,28 @@
         <v>12</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H63" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K63" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K63" s="2" t="s">
+      <c r="L63" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="N63" s="5" t="s">
-        <v>207</v>
+      <c r="N63" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -5741,21 +5730,21 @@
         <v>189</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>22</v>
@@ -5767,54 +5756,54 @@
         <v>13</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H64" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K64" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K64" s="2" t="s">
+      <c r="L64" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="L64" s="2" t="s">
+      <c r="M64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S64" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="65" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>22</v>
@@ -5826,25 +5815,25 @@
         <v>13</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K65" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="L65" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="M65" s="5" t="s">
-        <v>207</v>
+      <c r="M65" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="N65" s="3" t="s">
         <v>31</v>
@@ -5862,18 +5851,18 @@
         <v>28</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="66" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>22</v>
@@ -5885,25 +5874,25 @@
         <v>13</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H66" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K66" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K66" s="2" t="s">
+      <c r="L66" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="M66" s="5" t="s">
-        <v>207</v>
+      <c r="M66" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>31</v>
@@ -5921,18 +5910,18 @@
         <v>28</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>22</v>
@@ -5944,25 +5933,25 @@
         <v>13</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H67" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K67" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K67" s="2" t="s">
+      <c r="L67" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="M67" s="5" t="s">
-        <v>207</v>
+      <c r="M67" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="N67" s="3" t="s">
         <v>31</v>
@@ -5980,18 +5969,18 @@
         <v>28</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="68" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>22</v>
@@ -6006,51 +5995,51 @@
         <v>25</v>
       </c>
       <c r="H68" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I68" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="I68" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="K68" s="2" t="s">
+      <c r="L68" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="L68" s="2" t="s">
+      <c r="M68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S68" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="69" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>22</v>
@@ -6065,20 +6054,20 @@
         <v>25</v>
       </c>
       <c r="H69" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J69" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="I69" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J69" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="K69" s="2" t="s">
+      <c r="L69" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="L69" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="M69" s="2" t="s">
         <v>28</v>
       </c>
@@ -6098,18 +6087,18 @@
         <v>28</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="70" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>22</v>
@@ -6124,20 +6113,20 @@
         <v>25</v>
       </c>
       <c r="H70" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K70" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K70" s="2" t="s">
+      <c r="L70" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="M70" s="2" t="s">
         <v>28</v>
       </c>
@@ -6157,18 +6146,18 @@
         <v>28</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="71" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>22</v>
@@ -6183,20 +6172,20 @@
         <v>25</v>
       </c>
       <c r="H71" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K71" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K71" s="2" t="s">
+      <c r="L71" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="L71" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="M71" s="2" t="s">
         <v>28</v>
       </c>
@@ -6216,18 +6205,18 @@
         <v>28</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="72" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>22</v>
@@ -6242,20 +6231,20 @@
         <v>25</v>
       </c>
       <c r="H72" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J72" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J72" s="2" t="s">
+      <c r="K72" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="L72" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="L72" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="M72" s="2" t="s">
         <v>28</v>
       </c>
@@ -6275,18 +6264,18 @@
         <v>28</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="73" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>22</v>
@@ -6301,20 +6290,20 @@
         <v>25</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K73" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="L73" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="L73" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="M73" s="2" t="s">
         <v>28</v>
       </c>
@@ -6334,18 +6323,18 @@
         <v>28</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="74" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>68</v>
@@ -6360,20 +6349,20 @@
         <v>25</v>
       </c>
       <c r="H74" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K74" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K74" s="2" t="s">
+      <c r="L74" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="L74" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="M74" s="2" t="s">
         <v>28</v>
       </c>
@@ -6393,18 +6382,18 @@
         <v>28</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>22</v>
@@ -6419,51 +6408,51 @@
         <v>25</v>
       </c>
       <c r="H75" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K75" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K75" s="2" t="s">
+      <c r="L75" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="L75" s="2" t="s">
+      <c r="M75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S75" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S75" s="2" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="76" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>22</v>
@@ -6478,20 +6467,20 @@
         <v>25</v>
       </c>
       <c r="H76" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K76" s="2" t="s">
+      <c r="L76" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="M76" s="2" t="s">
         <v>28</v>
       </c>
@@ -6511,18 +6500,18 @@
         <v>28</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>22</v>
@@ -6537,20 +6526,20 @@
         <v>25</v>
       </c>
       <c r="H77" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K77" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K77" s="2" t="s">
+      <c r="L77" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="L77" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="M77" s="2" t="s">
         <v>28</v>
       </c>
@@ -6570,18 +6559,18 @@
         <v>28</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="78" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>55</v>
@@ -6596,20 +6585,20 @@
         <v>25</v>
       </c>
       <c r="H78" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K78" s="2" t="s">
+      <c r="L78" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L78" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="M78" s="2" t="s">
         <v>28</v>
       </c>
@@ -6629,18 +6618,18 @@
         <v>28</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="79" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>55</v>
@@ -6655,51 +6644,51 @@
         <v>25</v>
       </c>
       <c r="H79" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K79" s="2" t="s">
+      <c r="L79" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="L79" s="2" t="s">
+      <c r="M79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S79" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="80" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>55</v>
@@ -6714,20 +6703,20 @@
         <v>25</v>
       </c>
       <c r="H80" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K80" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K80" s="2" t="s">
+      <c r="L80" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>28</v>
       </c>
@@ -6747,18 +6736,18 @@
         <v>28</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="81" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>55</v>
@@ -6773,20 +6762,20 @@
         <v>25</v>
       </c>
       <c r="H81" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K81" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K81" s="2" t="s">
+      <c r="L81" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>483</v>
-      </c>
       <c r="M81" s="2" t="s">
         <v>28</v>
       </c>
@@ -6806,18 +6795,18 @@
         <v>28</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>55</v>
@@ -6832,20 +6821,20 @@
         <v>25</v>
       </c>
       <c r="H82" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K82" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="I82" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K82" s="2" t="s">
+      <c r="L82" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="M82" s="2" t="s">
         <v>28</v>
       </c>
@@ -6865,18 +6854,18 @@
         <v>28</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>40</v>
@@ -6891,20 +6880,20 @@
         <v>25</v>
       </c>
       <c r="H83" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K83" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K83" s="2" t="s">
+      <c r="L83" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="L83" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="M83" s="2" t="s">
         <v>28</v>
       </c>
@@ -6924,18 +6913,18 @@
         <v>28</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="84" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>55</v>
@@ -6950,20 +6939,20 @@
         <v>25</v>
       </c>
       <c r="H84" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K84" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K84" s="2" t="s">
+      <c r="L84" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="M84" s="2" t="s">
         <v>28</v>
       </c>
@@ -6983,18 +6972,18 @@
         <v>28</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="85" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>68</v>
@@ -7009,19 +6998,19 @@
         <v>25</v>
       </c>
       <c r="H85" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K85" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K85" s="2" t="s">
+      <c r="L85" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>28</v>
@@ -7039,21 +7028,21 @@
         <v>189</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="86" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>68</v>
@@ -7068,19 +7057,19 @@
         <v>25</v>
       </c>
       <c r="H86" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K86" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K86" s="2" t="s">
+      <c r="L86" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>28</v>
@@ -7098,10 +7087,10 @@
         <v>189</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="562">
   <si>
     <t>ID</t>
   </si>
@@ -112,7 +112,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>tests/web/home/home.spec.ts</t>
+    <t>tests/web/home/TC-HOME-001_Homepage_Loads.spec.ts</t>
   </si>
   <si>
     <t>TC-HOME-002</t>
@@ -131,6 +131,9 @@
     <t>Story page opens; its title matches the card title</t>
   </si>
   <si>
+    <t>tests/web/home/TC-HOME-002_Headline_Opens_Article.spec.ts</t>
+  </si>
+  <si>
     <t>TC-HOME-003</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
     <t>Logo and headlines visible and reachable</t>
   </si>
   <si>
+    <t>tests/web/home/TC-HOME-003_Usable_With_Ads_On.spec.ts</t>
+  </si>
+  <si>
     <t>TC-AUTH-001</t>
   </si>
   <si>
@@ -175,7 +181,7 @@
     <t>/login shows email, password (masked) and the submit button</t>
   </si>
   <si>
-    <t>tests/web/auth/login.spec.ts</t>
+    <t>tests/web/auth/TC-AUTH-001_Login_Entry_Opens_Form.spec.ts</t>
   </si>
   <si>
     <t>TC-AUTH-002</t>
@@ -197,6 +203,9 @@
   </si>
   <si>
     <t>Fields empty; "Masuk" disabled</t>
+  </si>
+  <si>
+    <t>tests/web/auth/TC-AUTH-002_Submit_Disabled_When_Empty.spec.ts</t>
   </si>
   <si>
     <t>TC-AUTH-003</t>
@@ -219,6 +228,9 @@
     <t>"Harus diisi dengan format email" shown; submit disabled</t>
   </si>
   <si>
+    <t>tests/web/auth/TC-AUTH-003_Malformed_Email_Rejected.spec.ts</t>
+  </si>
+  <si>
     <t>TC-AUTH-004</t>
   </si>
   <si>
@@ -239,6 +251,9 @@
     <t>"Tidak boleh kosong" under password; submit disabled</t>
   </si>
   <si>
+    <t>tests/web/auth/TC-AUTH-004_Cleared_Password_Required.spec.ts</t>
+  </si>
+  <si>
     <t>TC-AUTH-005</t>
   </si>
   <si>
@@ -253,6 +268,9 @@
   </si>
   <si>
     <t>Cloudflare Turnstile present; submit stays disabled</t>
+  </si>
+  <si>
+    <t>tests/web/auth/TC-AUTH-005_Bot_Challenge_Before_Submit.spec.ts</t>
   </si>
   <si>
     <t>TC-AUTH-006</t>
@@ -275,6 +293,9 @@
     <t>Field type text then password; value unchanged</t>
   </si>
   <si>
+    <t>tests/web/auth/TC-AUTH-006_Password_Visibility_Toggle.spec.ts</t>
+  </si>
+  <si>
     <t>TC-AUTH-007</t>
   </si>
   <si>
@@ -290,6 +311,9 @@
     <t>Facebook, Google, phone sign-in, "Lupa Password" and "Daftar Sekarang!" visible</t>
   </si>
   <si>
+    <t>tests/web/auth/TC-AUTH-007_Alternative_Sign_In_Options.spec.ts</t>
+  </si>
+  <si>
     <t>TC-ART-001</t>
   </si>
   <si>
@@ -311,7 +335,7 @@
     <t>Title, author, channel, publish date and more than one paragraph present</t>
   </si>
   <si>
-    <t>tests/web/article/article.spec.ts</t>
+    <t>tests/web/article/TC-ART-001_Story_Content_Shown.spec.ts</t>
   </si>
   <si>
     <t>TC-ART-002</t>
@@ -326,6 +350,9 @@
     <t>Like, comment, share and report present; counters are numbers</t>
   </si>
   <si>
+    <t>tests/web/article/TC-ART-002_Engagement_Bar_Shown.spec.ts</t>
+  </si>
+  <si>
     <t>TC-ART-003</t>
   </si>
   <si>
@@ -338,6 +365,9 @@
     <t>&lt;title&gt; starts with the headline and ends "| kumparan.com"; canonical ends with the story slug</t>
   </si>
   <si>
+    <t>tests/web/article/TC-ART-003_Title_And_Canonical_Match_Story.spec.ts</t>
+  </si>
+  <si>
     <t>TC-ART-004</t>
   </si>
   <si>
@@ -351,6 +381,9 @@
   </si>
   <si>
     <t>HTTP 404; header still usable</t>
+  </si>
+  <si>
+    <t>tests/web/article/TC-ART-004_Unknown_Story_Returns_404.spec.ts</t>
   </si>
   <si>
     <t>TC-ART-005</t>
@@ -367,6 +400,9 @@
   </si>
   <si>
     <t>Homepage with headlines</t>
+  </si>
+  <si>
+    <t>tests/web/article/TC-ART-005_Breadcrumb_Returns_Home.spec.ts</t>
   </si>
   <si>
     <t>TC-LIKE-004</t>
@@ -389,7 +425,7 @@
     <t>Redirect to /login; like count unchanged</t>
   </si>
   <si>
-    <t>tests/web/engagement/like.spec.ts</t>
+    <t>tests/web/like/TC-LIKE-004_Guest_Like_Redirects_To_Login.spec.ts</t>
   </si>
   <si>
     <t>TC-CMT-001</t>
@@ -411,7 +447,7 @@
     <t>/&lt;channel&gt;/response/&lt;slug&gt; with the story card, editor "Tulis komentar..." and send button</t>
   </si>
   <si>
-    <t>tests/web/engagement/comment.spec.ts</t>
+    <t>tests/web/comment/TC-CMT-001_Comment_Button_Opens_Thread.spec.ts</t>
   </si>
   <si>
     <t>TC-CMT-002</t>
@@ -430,6 +466,9 @@
     <t>Thread header shows "&lt;same count&gt; Komentar"; empty state when 0</t>
   </si>
   <si>
+    <t>tests/web/comment/TC-CMT-002_Comment_Count_Matches_Thread.spec.ts</t>
+  </si>
+  <si>
     <t>TC-CMT-004</t>
   </si>
   <si>
@@ -446,6 +485,9 @@
     <t>No comment mutation sent; still on the thread. Observation OBS-001: no login prompt while drafting</t>
   </si>
   <si>
+    <t>tests/web/comment/TC-CMT-004_Guest_Draft_Publishes_Nothing.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-001</t>
   </si>
   <si>
@@ -465,7 +507,7 @@
     <t>Form shows the story and the six reasons</t>
   </si>
   <si>
-    <t>tests/web/engagement/report.spec.ts</t>
+    <t>tests/web/report/TC-RPT-001_Report_Form_Shows_Six_Reasons.spec.ts</t>
   </si>
   <si>
     <t>TC-RPT-002</t>
@@ -489,6 +531,9 @@
     <t>Reason checked; "Laporkan" enabled. Not clicked</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-002_Each_Reason_Enables_Submit.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-003</t>
   </si>
   <si>
@@ -502,6 +547,9 @@
   </si>
   <si>
     <t>"Laporkan" disabled</t>
+  </si>
+  <si>
+    <t>tests/web/report/TC-RPT-003_Submit_Disabled_Without_Reason.spec.ts</t>
   </si>
   <si>
     <t>TC-RPT-004</t>
@@ -523,6 +571,9 @@
     <t>Back on the story</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-004_Cancel_Returns_To_Story.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-005</t>
   </si>
   <si>
@@ -539,6 +590,9 @@
     <t>Only reason 4 checked</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-005_Only_One_Reason_Selected.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-006</t>
   </si>
   <si>
@@ -552,6 +606,9 @@
   </si>
   <si>
     <t>Free-text field appears</t>
+  </si>
+  <si>
+    <t>tests/web/report/TC-RPT-006_Other_Reveals_Text_Field.spec.ts</t>
   </si>
   <si>
     <t>TC-RPT-007</t>
@@ -570,6 +627,9 @@
     <t>"Laporkan" enabled for a guest (server behavior on submit not verifiable: submitting is forbidden)</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-007_Guest_Reaches_Enabled_Submit.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-008</t>
   </si>
   <si>
@@ -583,6 +643,9 @@
   </si>
   <si>
     <t>No 5xx; no blank page; no story card</t>
+  </si>
+  <si>
+    <t>tests/web/report/TC-RPT-008_Missing_Story_Handled.spec.ts</t>
   </si>
   <si>
     <t>TC-RPT-009</t>
@@ -610,6 +673,9 @@
     <t>BUG-001</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-009_Cancel_In_New_Tab_Leaves_Form.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-010</t>
   </si>
   <si>
@@ -623,6 +689,9 @@
 2. Leave the text empty</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-010_Other_Empty_Cannot_Submit.spec.ts</t>
+  </si>
+  <si>
     <t>TC-RPT-011</t>
   </si>
   <si>
@@ -640,6 +709,9 @@
   </si>
   <si>
     <t>"Laporkan" enabled. Not clicked</t>
+  </si>
+  <si>
+    <t>tests/web/report/TC-RPT-011_Other_With_Text_Can_Submit.spec.ts</t>
   </si>
   <si>
     <t>TC-RPT-012</t>
@@ -665,6 +737,9 @@
     <t>BUG-002</t>
   </si>
   <si>
+    <t>tests/web/report/TC-RPT-012_Keyboard_Report_Keeps_Form_Url.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SHR-001</t>
   </si>
   <si>
@@ -684,7 +759,7 @@
     <t>api.whatsapp.com popup whose text has the headline and kumparan.com/&lt;channel&gt;/&lt;story-id&gt;</t>
   </si>
   <si>
-    <t>tests/web/engagement/share.spec.ts</t>
+    <t>tests/web/share/TC-SHR-001_WhatsApp_Share_Carries_Story.spec.ts</t>
   </si>
   <si>
     <t>TC-SHR-002</t>
@@ -703,6 +778,9 @@
     <t>WhatsApp, Facebook, X, LINE and copy-link options visible</t>
   </si>
   <si>
+    <t>tests/web/share/TC-SHR-002_Share_Menu_Lists_Channels.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SHR-003</t>
   </si>
   <si>
@@ -722,6 +800,9 @@
     <t>"URL berhasil disalin" shown; clipboard holds https://kumparan.com/&lt;channel&gt;/&lt;story-id&gt;?…</t>
   </si>
   <si>
+    <t>tests/web/share/TC-SHR-003_Copy_Link_Copies_Story.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SHR-004</t>
   </si>
   <si>
@@ -740,6 +821,9 @@
     <t>Popup to the channel host containing the story id</t>
   </si>
   <si>
+    <t>tests/web/share/TC-SHR-004_Menu_Shares_Carry_Story.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SHR-005</t>
   </si>
   <si>
@@ -755,6 +839,9 @@
     <t>Link starts with https://kumparan.com/</t>
   </si>
   <si>
+    <t>tests/web/share/TC-SHR-005_Shared_Links_Are_Absolute.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SHR-006</t>
   </si>
   <si>
@@ -770,6 +857,9 @@
     <t>Menu hidden; still on the story</t>
   </si>
   <si>
+    <t>tests/web/share/TC-SHR-006_Share_Menu_Closes.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-001</t>
   </si>
   <si>
@@ -791,7 +881,7 @@
     <t>/search/banjir with results; top titles mention the keyword</t>
   </si>
   <si>
-    <t>tests/web/search/search.spec.ts</t>
+    <t>tests/web/search/TC-SRCH-001_Keyword_Returns_Relevant_Stories.spec.ts</t>
   </si>
   <si>
     <t>TC-SRCH-002</t>
@@ -812,6 +902,9 @@
     <t>URL /search/banjir/&lt;video|collection|topik|user|publisher&gt; with that card type</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-002_Tabs_Switch_Result_Type.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-003</t>
   </si>
   <si>
@@ -827,6 +920,9 @@
     <t>Terbaru active, Relevansi inactive, results shown</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-003_Sort_By_Newest.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-004</t>
   </si>
   <si>
@@ -845,6 +941,9 @@
     <t>0 results; "Story tidak ditemukan"</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-004_Nonsense_Keyword_Not_Found.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-005</t>
   </si>
   <si>
@@ -860,6 +959,9 @@
     <t>/search with no results</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-005_Empty_Query_Stays_On_Landing.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-006</t>
   </si>
   <si>
@@ -878,6 +980,9 @@
     <t>Results or the not-found state; no error</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-006_One_Character_Query.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-007</t>
   </si>
   <si>
@@ -896,6 +1001,9 @@
     <t>No 5xx; results or not-found state</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-007_Long_Query_Handled.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-008</t>
   </si>
   <si>
@@ -914,6 +1022,9 @@
     <t>URL-encoded query; no &lt;b&gt; element with the probe text in the page</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-008_Html_Shown_As_Text.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-009</t>
   </si>
   <si>
@@ -932,6 +1043,9 @@
     <t>URL contains %F0%9F%99%82; results or not-found</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-009_Emoji_Query_Encoded.spec.ts</t>
+  </si>
+  <si>
     <t>TC-SRCH-010</t>
   </si>
   <si>
@@ -950,6 +1064,9 @@
     <t>/search/food%20%26%20travel with results</t>
   </si>
   <si>
+    <t>tests/web/search/TC-SRCH-010_Ampersand_Query_Encoded.spec.ts</t>
+  </si>
+  <si>
     <t>TC-NAV-001</t>
   </si>
   <si>
@@ -968,7 +1085,7 @@
     <t>/channel/news with channel content</t>
   </si>
   <si>
-    <t>tests/web/navigation/navigation.spec.ts</t>
+    <t>tests/web/navigation/TC-NAV-001_Channel_Menu_Opens_News.spec.ts</t>
   </si>
   <si>
     <t>TC-NAV-002</t>
@@ -990,6 +1107,9 @@
     <t>Drawer slides in with "Mode Gelap", then out</t>
   </si>
   <si>
+    <t>tests/web/navigation/TC-NAV-002_Mobile_Side_Menu_Opens_Closes.spec.ts</t>
+  </si>
+  <si>
     <t>TC-NAV-003</t>
   </si>
   <si>
@@ -1009,6 +1129,9 @@
     <t>Body background rgb(24,24,24); localStorage theme=dark; still dark after reload</t>
   </si>
   <si>
+    <t>tests/web/navigation/TC-NAV-003_Dark_Mode_Survives_Reload.spec.ts</t>
+  </si>
+  <si>
     <t>TC-NAV-004</t>
   </si>
   <si>
@@ -1025,6 +1148,9 @@
   </si>
   <si>
     <t>/trending with trending stories</t>
+  </si>
+  <si>
+    <t>tests/web/navigation/TC-NAV-004_Trending_From_Load_More.spec.ts</t>
   </si>
   <si>
     <t>TC-NAV-005</t>
@@ -1046,6 +1172,9 @@
     <t>BUG-003</t>
   </si>
   <si>
+    <t>tests/web/navigation/TC-NAV-005_No_JavaScript_Errors.spec.ts</t>
+  </si>
+  <si>
     <t>TC-NAV-006</t>
   </si>
   <si>
@@ -1056,6 +1185,9 @@
   </si>
   <si>
     <t>1. Tap "Trending" in the top-nav strip</t>
+  </si>
+  <si>
+    <t>tests/web/navigation/TC-NAV-006_Mobile_Top_Nav_Opens_Trending.spec.ts</t>
   </si>
   <si>
     <t>TC-AGT-001</t>
@@ -2227,24 +2359,24 @@
         <v>29</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>25</v>
@@ -2253,19 +2385,19 @@
         <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>32</v>
@@ -2289,18 +2421,18 @@
         <v>29</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>23</v>
@@ -2315,7 +2447,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>28</v>
@@ -2324,10 +2456,10 @@
         <v>29</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>32</v>
@@ -2351,21 +2483,21 @@
         <v>29</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>24</v>
@@ -2377,19 +2509,19 @@
         <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>32</v>
@@ -2413,21 +2545,21 @@
         <v>29</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>24</v>
@@ -2439,19 +2571,19 @@
         <v>26</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>32</v>
@@ -2475,24 +2607,24 @@
         <v>29</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>25</v>
@@ -2501,19 +2633,19 @@
         <v>26</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>32</v>
@@ -2537,24 +2669,24 @@
         <v>29</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>25</v>
@@ -2563,19 +2695,19 @@
         <v>26</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>32</v>
@@ -2599,24 +2731,24 @@
         <v>29</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>25</v>
@@ -2625,19 +2757,19 @@
         <v>26</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>32</v>
@@ -2661,24 +2793,24 @@
         <v>29</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>25</v>
@@ -2687,19 +2819,19 @@
         <v>26</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>32</v>
@@ -2723,18 +2855,18 @@
         <v>29</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>23</v>
@@ -2749,19 +2881,19 @@
         <v>26</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>32</v>
@@ -2785,18 +2917,18 @@
         <v>29</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>23</v>
@@ -2811,19 +2943,19 @@
         <v>26</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>32</v>
@@ -2847,24 +2979,24 @@
         <v>29</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>25</v>
@@ -2873,19 +3005,19 @@
         <v>26</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>32</v>
@@ -2909,24 +3041,24 @@
         <v>29</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>25</v>
@@ -2935,7 +3067,7 @@
         <v>26</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>28</v>
@@ -2944,10 +3076,10 @@
         <v>29</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>32</v>
@@ -2971,24 +3103,24 @@
         <v>29</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>25</v>
@@ -2997,19 +3129,19 @@
         <v>26</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>32</v>
@@ -3033,21 +3165,21 @@
         <v>29</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>24</v>
@@ -3059,19 +3191,19 @@
         <v>26</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>32</v>
@@ -3095,18 +3227,18 @@
         <v>29</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>23</v>
@@ -3121,19 +3253,19 @@
         <v>26</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>32</v>
@@ -3157,24 +3289,24 @@
         <v>29</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>25</v>
@@ -3183,19 +3315,19 @@
         <v>26</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>32</v>
@@ -3219,21 +3351,21 @@
         <v>29</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>24</v>
@@ -3245,19 +3377,19 @@
         <v>26</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>32</v>
@@ -3281,18 +3413,18 @@
         <v>29</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>23</v>
@@ -3307,19 +3439,19 @@
         <v>26</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>32</v>
@@ -3343,18 +3475,18 @@
         <v>29</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>23</v>
@@ -3369,19 +3501,19 @@
         <v>26</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>32</v>
@@ -3405,21 +3537,21 @@
         <v>29</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>24</v>
@@ -3431,19 +3563,19 @@
         <v>26</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>32</v>
@@ -3467,24 +3599,24 @@
         <v>29</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>25</v>
@@ -3493,19 +3625,19 @@
         <v>26</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>32</v>
@@ -3529,24 +3661,24 @@
         <v>29</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>25</v>
@@ -3555,19 +3687,19 @@
         <v>26</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>32</v>
@@ -3591,24 +3723,24 @@
         <v>29</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>25</v>
@@ -3617,19 +3749,19 @@
         <v>26</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>32</v>
@@ -3653,21 +3785,21 @@
         <v>29</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>24</v>
@@ -3679,7 +3811,7 @@
         <v>26</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>28</v>
@@ -3688,10 +3820,10 @@
         <v>29</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>32</v>
@@ -3715,24 +3847,24 @@
         <v>29</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>25</v>
@@ -3741,7 +3873,7 @@
         <v>26</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>28</v>
@@ -3750,10 +3882,10 @@
         <v>29</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>32</v>
@@ -3777,24 +3909,24 @@
         <v>29</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>25</v>
@@ -3803,25 +3935,25 @@
         <v>26</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>29</v>
@@ -3830,33 +3962,33 @@
         <v>29</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="S29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>25</v>
@@ -3865,19 +3997,19 @@
         <v>26</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>32</v>
@@ -3901,24 +4033,24 @@
         <v>29</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>145</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>25</v>
@@ -3927,19 +4059,19 @@
         <v>26</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>32</v>
@@ -3963,24 +4095,24 @@
         <v>29</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>12</v>
@@ -3989,22 +4121,22 @@
         <v>26</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>29</v>
@@ -4016,27 +4148,27 @@
         <v>29</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="S32" s="2" t="s">
         <v>29</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>145</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>23</v>
@@ -4051,19 +4183,19 @@
         <v>26</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>32</v>
@@ -4087,24 +4219,24 @@
         <v>29</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>25</v>
@@ -4113,19 +4245,19 @@
         <v>26</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>32</v>
@@ -4149,18 +4281,18 @@
         <v>29</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>23</v>
@@ -4175,19 +4307,19 @@
         <v>26</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>32</v>
@@ -4211,24 +4343,24 @@
         <v>29</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>25</v>
@@ -4237,19 +4369,19 @@
         <v>26</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>32</v>
@@ -4273,24 +4405,24 @@
         <v>29</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>25</v>
@@ -4299,7 +4431,7 @@
         <v>26</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>28</v>
@@ -4308,10 +4440,10 @@
         <v>29</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>32</v>
@@ -4335,24 +4467,24 @@
         <v>29</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>25</v>
@@ -4361,19 +4493,19 @@
         <v>26</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>241</v>
+        <v>270</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>32</v>
@@ -4397,18 +4529,18 @@
         <v>29</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>215</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>23</v>
@@ -4423,19 +4555,19 @@
         <v>26</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>32</v>
@@ -4459,24 +4591,24 @@
         <v>29</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>25</v>
@@ -4485,19 +4617,19 @@
         <v>26</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>32</v>
@@ -4521,24 +4653,24 @@
         <v>29</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>25</v>
@@ -4547,19 +4679,19 @@
         <v>26</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>32</v>
@@ -4583,24 +4715,24 @@
         <v>29</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>25</v>
@@ -4609,19 +4741,19 @@
         <v>26</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>32</v>
@@ -4645,24 +4777,24 @@
         <v>29</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>25</v>
@@ -4671,7 +4803,7 @@
         <v>26</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>28</v>
@@ -4680,10 +4812,10 @@
         <v>29</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>32</v>
@@ -4707,24 +4839,24 @@
         <v>29</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>25</v>
@@ -4733,19 +4865,19 @@
         <v>26</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>32</v>
@@ -4769,24 +4901,24 @@
         <v>29</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>250</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>25</v>
@@ -4795,19 +4927,19 @@
         <v>26</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>32</v>
@@ -4831,21 +4963,21 @@
         <v>29</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>24</v>
@@ -4857,19 +4989,19 @@
         <v>26</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>32</v>
@@ -4893,24 +5025,24 @@
         <v>29</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>250</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>291</v>
+        <v>328</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>292</v>
+        <v>329</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>25</v>
@@ -4919,19 +5051,19 @@
         <v>26</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>293</v>
+        <v>330</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>32</v>
@@ -4955,24 +5087,24 @@
         <v>29</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>25</v>
@@ -4981,19 +5113,19 @@
         <v>26</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>28</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>32</v>
@@ -5017,24 +5149,24 @@
         <v>29</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>250</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>305</v>
+        <v>344</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>25</v>
@@ -5043,7 +5175,7 @@
         <v>26</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>306</v>
+        <v>345</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>28</v>
@@ -5052,10 +5184,10 @@
         <v>29</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>32</v>
@@ -5079,24 +5211,24 @@
         <v>29</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>309</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>13</v>
@@ -5105,19 +5237,19 @@
         <v>26</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>29</v>
@@ -5141,24 +5273,24 @@
         <v>29</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>317</v>
+        <v>357</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>25</v>
@@ -5167,19 +5299,19 @@
         <v>26</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>319</v>
+        <v>359</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>321</v>
+        <v>361</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>32</v>
@@ -5203,24 +5335,24 @@
         <v>29</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>309</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>12</v>
@@ -5229,19 +5361,19 @@
         <v>26</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>325</v>
+        <v>366</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>32</v>
@@ -5265,24 +5397,24 @@
         <v>29</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>309</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>329</v>
+        <v>371</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>25</v>
@@ -5291,7 +5423,7 @@
         <v>26</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>28</v>
@@ -5300,13 +5432,13 @@
         <v>29</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>331</v>
+        <v>373</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>332</v>
+        <v>374</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>32</v>
@@ -5318,33 +5450,33 @@
         <v>29</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
       <c r="S53" s="2" t="s">
         <v>29</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>309</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>13</v>
@@ -5353,19 +5485,19 @@
         <v>26</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>337</v>
+        <v>380</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>29</v>
@@ -5389,33 +5521,33 @@
         <v>29</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>309</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>28</v>
@@ -5424,10 +5556,10 @@
         <v>29</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>343</v>
+        <v>387</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>32</v>
@@ -5448,36 +5580,36 @@
         <v>29</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>345</v>
+        <v>389</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>28</v>
@@ -5486,10 +5618,10 @@
         <v>29</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>32</v>
@@ -5510,36 +5642,36 @@
         <v>29</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>351</v>
+        <v>395</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>28</v>
@@ -5548,10 +5680,10 @@
         <v>29</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>32</v>
@@ -5572,36 +5704,36 @@
         <v>29</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>28</v>
@@ -5610,10 +5742,10 @@
         <v>29</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>32</v>
@@ -5634,21 +5766,21 @@
         <v>29</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>23</v>
@@ -5660,10 +5792,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>28</v>
@@ -5672,10 +5804,10 @@
         <v>29</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>32</v>
@@ -5696,36 +5828,36 @@
         <v>29</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
     </row>
     <row r="60" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>370</v>
+        <v>414</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>28</v>
@@ -5734,10 +5866,10 @@
         <v>29</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>371</v>
+        <v>415</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>32</v>
@@ -5758,36 +5890,36 @@
         <v>29</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
     </row>
     <row r="61" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>28</v>
@@ -5796,10 +5928,10 @@
         <v>29</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>32</v>
@@ -5820,36 +5952,36 @@
         <v>29</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="62" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>28</v>
@@ -5858,10 +5990,10 @@
         <v>29</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>32</v>
@@ -5882,51 +6014,51 @@
         <v>29</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
     </row>
     <row r="63" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>387</v>
+        <v>431</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>29</v>
@@ -5938,54 +6070,54 @@
         <v>29</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>391</v>
+        <v>435</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
     </row>
     <row r="64" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>29</v>
@@ -6006,48 +6138,48 @@
         <v>29</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
     </row>
     <row r="65" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>400</v>
+        <v>444</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>401</v>
+        <v>445</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>29</v>
@@ -6068,21 +6200,21 @@
         <v>29</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
     </row>
     <row r="66" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>23</v>
@@ -6094,22 +6226,22 @@
         <v>13</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>29</v>
@@ -6130,21 +6262,21 @@
         <v>29</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
     </row>
     <row r="67" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>23</v>
@@ -6156,22 +6288,22 @@
         <v>13</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>411</v>
+        <v>455</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>29</v>
@@ -6192,21 +6324,21 @@
         <v>29</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
     </row>
     <row r="68" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>414</v>
+        <v>458</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>23</v>
@@ -6221,19 +6353,19 @@
         <v>26</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>29</v>
@@ -6257,18 +6389,18 @@
         <v>29</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>23</v>
@@ -6283,19 +6415,19 @@
         <v>26</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>29</v>
@@ -6319,18 +6451,18 @@
         <v>29</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="70" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>429</v>
+        <v>473</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>430</v>
+        <v>474</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>23</v>
@@ -6345,19 +6477,19 @@
         <v>26</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>431</v>
+        <v>475</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>432</v>
+        <v>476</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>433</v>
+        <v>477</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>29</v>
@@ -6381,24 +6513,24 @@
         <v>29</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="71" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>15</v>
@@ -6407,19 +6539,19 @@
         <v>26</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>437</v>
+        <v>481</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>29</v>
@@ -6443,24 +6575,24 @@
         <v>29</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="72" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>439</v>
+        <v>483</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>15</v>
@@ -6469,19 +6601,19 @@
         <v>26</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>443</v>
+        <v>487</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>444</v>
+        <v>488</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>29</v>
@@ -6505,24 +6637,24 @@
         <v>29</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>445</v>
+        <v>489</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>446</v>
+        <v>490</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>15</v>
@@ -6531,19 +6663,19 @@
         <v>26</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>29</v>
@@ -6567,24 +6699,24 @@
         <v>29</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="74" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>449</v>
+        <v>493</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>15</v>
@@ -6593,19 +6725,19 @@
         <v>26</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>452</v>
+        <v>496</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>453</v>
+        <v>497</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>29</v>
@@ -6629,18 +6761,18 @@
         <v>29</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>454</v>
+        <v>498</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>455</v>
+        <v>499</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>23</v>
@@ -6655,19 +6787,19 @@
         <v>26</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>456</v>
+        <v>500</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>457</v>
+        <v>501</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>458</v>
+        <v>502</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>29</v>
@@ -6691,18 +6823,18 @@
         <v>29</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>459</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>460</v>
+        <v>504</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>461</v>
+        <v>505</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>23</v>
@@ -6717,19 +6849,19 @@
         <v>26</v>
       </c>
       <c r="H76" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="I76" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>418</v>
-      </c>
       <c r="J76" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>463</v>
+        <v>507</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>464</v>
+        <v>508</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>29</v>
@@ -6753,18 +6885,18 @@
         <v>29</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>459</v>
+        <v>503</v>
       </c>
     </row>
     <row r="77" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>465</v>
+        <v>509</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>466</v>
+        <v>510</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>23</v>
@@ -6779,19 +6911,19 @@
         <v>26</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>468</v>
+        <v>512</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>469</v>
+        <v>513</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>29</v>
@@ -6815,21 +6947,21 @@
         <v>29</v>
       </c>
       <c r="T77" s="2" t="s">
-        <v>459</v>
+        <v>503</v>
       </c>
     </row>
     <row r="78" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>470</v>
+        <v>514</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>471</v>
+        <v>515</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>24</v>
@@ -6841,19 +6973,19 @@
         <v>26</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>472</v>
+        <v>516</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>473</v>
+        <v>517</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>474</v>
+        <v>518</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>29</v>
@@ -6877,21 +7009,21 @@
         <v>29</v>
       </c>
       <c r="T78" s="2" t="s">
-        <v>459</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>475</v>
+        <v>519</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>476</v>
+        <v>520</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>24</v>
@@ -6903,19 +7035,19 @@
         <v>26</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>477</v>
+        <v>521</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>478</v>
+        <v>522</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>479</v>
+        <v>523</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>29</v>
@@ -6939,21 +7071,21 @@
         <v>29</v>
       </c>
       <c r="T79" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="80" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>481</v>
+        <v>525</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>482</v>
+        <v>526</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>24</v>
@@ -6965,19 +7097,19 @@
         <v>26</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>483</v>
+        <v>527</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>484</v>
+        <v>528</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>485</v>
+        <v>529</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>29</v>
@@ -7001,21 +7133,21 @@
         <v>29</v>
       </c>
       <c r="T80" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="81" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>486</v>
+        <v>530</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>487</v>
+        <v>531</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>24</v>
@@ -7027,19 +7159,19 @@
         <v>26</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>488</v>
+        <v>532</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>489</v>
+        <v>533</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>490</v>
+        <v>534</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>29</v>
@@ -7063,24 +7195,24 @@
         <v>29</v>
       </c>
       <c r="T81" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="82" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>491</v>
+        <v>535</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>492</v>
+        <v>536</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>15</v>
@@ -7089,19 +7221,19 @@
         <v>26</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>493</v>
+        <v>537</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>495</v>
+        <v>539</v>
       </c>
       <c r="M82" s="2" t="s">
         <v>29</v>
@@ -7125,21 +7257,21 @@
         <v>29</v>
       </c>
       <c r="T82" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="83" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>496</v>
+        <v>540</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>497</v>
+        <v>541</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>24</v>
@@ -7151,19 +7283,19 @@
         <v>26</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>500</v>
+        <v>544</v>
       </c>
       <c r="M83" s="2" t="s">
         <v>29</v>
@@ -7187,24 +7319,24 @@
         <v>29</v>
       </c>
       <c r="T83" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="84" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>501</v>
+        <v>545</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>502</v>
+        <v>546</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>15</v>
@@ -7213,19 +7345,19 @@
         <v>26</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>503</v>
+        <v>547</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>504</v>
+        <v>548</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>505</v>
+        <v>549</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>29</v>
@@ -7249,24 +7381,24 @@
         <v>29</v>
       </c>
       <c r="T84" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="85" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>506</v>
+        <v>550</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>507</v>
+        <v>551</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>15</v>
@@ -7275,19 +7407,19 @@
         <v>26</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>508</v>
+        <v>552</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>509</v>
+        <v>553</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>510</v>
+        <v>554</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>29</v>
@@ -7299,36 +7431,36 @@
         <v>29</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="Q85" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="S85" s="2" t="s">
         <v>29</v>
       </c>
       <c r="T85" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
     <row r="86" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>513</v>
+        <v>557</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>15</v>
@@ -7337,19 +7469,19 @@
         <v>26</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>514</v>
+        <v>558</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>515</v>
+        <v>559</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>516</v>
+        <v>560</v>
       </c>
       <c r="M86" s="2" t="s">
         <v>29</v>
@@ -7361,19 +7493,19 @@
         <v>29</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>517</v>
+        <v>561</v>
       </c>
       <c r="S86" s="2" t="s">
         <v>29</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>480</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
